--- a/data/tags/סינגלים חדשים/global/2026-04-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-04-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מתנאל סבח - שריטות ופחדים קאבר</v>
+        <v>תמר אופיר – בדמייך חיי</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410322&amp;sid=43fe725fde6d02927362e89be5d6c20b</v>
+        <v>https://yosmusic.com/%d7%aa%d7%9e%d7%a8-%d7%90%d7%95%d7%a4%d7%99%d7%a8-%d7%91%d7%93%d7%9e%d7%99%d7%99%d7%9a-%d7%97%d7%99%d7%99/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>השיר בדמייך חיי בביצועה של תמר אופיר, המבוסס על הפסוקים “ואעבור עלייך…” מתוך ספר יחזקאל (שנכנסו גם לנוסח ההגדה), הוא דוגמה יפה לשילוב בין טקסט מקראי טעון לבין פרשנות מוזיקלית עכשווית, רגשית ואינטימית. המילים מהוות ביטוי עוצמתי לקידוש החיים מתוך</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,50 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מתנאל סבח - שריטות ופחדים קאבר</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>ליאור כהן - חוזה לך ברח קאבר</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-04-01</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410321&amp;sid=43fe725fde6d02927362e89be5d6c20b</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-04-01</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>ליאור כהן - חוזה לך ברח קאבר</v>
+        <v>תמר אופיר – בדמייך חיי</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-04-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-04-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>תמר אופיר – בדמייך חיי</v>
+        <v>ספיר יהודה לוי - מי המציא את המילה קאבר</v>
       </c>
       <c r="B2" t="str">
         <v>2026-04-02</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%aa%d7%9e%d7%a8-%d7%90%d7%95%d7%a4%d7%99%d7%a8-%d7%91%d7%93%d7%9e%d7%99%d7%99%d7%9a-%d7%97%d7%99%d7%99/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410326&amp;sid=6b30857c35a09382fab931eb4f860fc2</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-02</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר בדמייך חיי בביצועה של תמר אופיר, המבוסס על הפסוקים “ואעבור עלייך…” מתוך ספר יחזקאל (שנכנסו גם לנוסח ההגדה), הוא דוגמה יפה לשילוב בין טקסט מקראי טעון לבין פרשנות מוזיקלית עכשווית, רגשית ואינטימית. המילים מהוות ביטוי עוצמתי לקידוש החיים מתוך</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,126 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>תמר אופיר – בדמייך חיי</v>
+        <v>ספיר יהודה לוי - מי המציא את המילה קאבר</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>נתנאל ששון - היא יודעת קאבר</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-04-02</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410325&amp;sid=6b30857c35a09382fab931eb4f860fc2</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-04-02</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>נתנאל ששון - היא יודעת קאבר</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>נהוראי אברהם - מישל קאבר</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-04-02</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410324&amp;sid=6b30857c35a09382fab931eb4f860fc2</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-04-02</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>נהוראי אברהם - מישל קאבר</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>נאור כהן - להינשא הלילה &amp; תפילות קאבר</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-04-02</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410323&amp;sid=6b30857c35a09382fab931eb4f860fc2</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-04-02</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>נאור כהן - להינשא הלילה &amp; תפילות קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-04-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-04-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ספיר יהודה לוי - מי המציא את המילה קאבר</v>
+        <v>שילה שטראל - תקופה שלמה</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410326&amp;sid=6b30857c35a09382fab931eb4f860fc2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410340&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ספיר יהודה לוי - מי המציא את המילה קאבר</v>
+        <v>שילה שטראל - תקופה שלמה</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>נתנאל ששון - היא יודעת קאבר</v>
+        <v>רון סויסה - האור בחשכה</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410325&amp;sid=6b30857c35a09382fab931eb4f860fc2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410339&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>נתנאל ששון - היא יודעת קאבר</v>
+        <v>רון סויסה - האור בחשכה</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>נהוראי אברהם - מישל קאבר</v>
+        <v>ישראל בניטה - מי אני</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410324&amp;sid=6b30857c35a09382fab931eb4f860fc2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410338&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>נהוראי אברהם - מישל קאבר</v>
+        <v>ישראל בניטה - מי אני</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>נאור כהן - להינשא הלילה &amp; תפילות קאבר</v>
+        <v>יהונתן לוי - הסתכלת לי בעיניים</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410323&amp;sid=6b30857c35a09382fab931eb4f860fc2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410337&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,12 +583,392 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>נאור כהן - להינשא הלילה &amp; תפילות קאבר</v>
+        <v>יהונתן לוי - הסתכלת לי בעיניים</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>יהונתן חוטה - מחרוזת אבות ובנים 2026</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-04-03</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410336&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-04-03</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>יהונתן חוטה - מחרוזת אבות ובנים 2026</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>טלי רבקה סימן טוב - חיים חדשים</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-04-03</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410335&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-04-03</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>טלי רבקה סימן טוב - חיים חדשים</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>חי ברוך &amp; הרב ראובן אלבז - אור של תשובה</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-04-03</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410334&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-04-03</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>חי ברוך &amp; הרב ראובן אלבז - אור של תשובה</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>גל סינואני - יום יפה</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-04-03</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410333&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-04-03</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>גל סינואני - יום יפה</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>גל אדם - כבר לא שלך</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-04-03</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410332&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-04-03</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>גל אדם - כבר לא שלך</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>בנאל בן ציון - מאשאפ עוד נשימה &amp; היא יודעת</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-04-03</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410331&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-04-03</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>בנאל בן ציון - מאשאפ עוד נשימה &amp; היא יודעת</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>בועז טביב - מחרוזת ואסיליס קאראס 2026</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-04-03</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410330&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-04-03</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>בועז טביב - מחרוזת ואסיליס קאראס 2026</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>אליאור נונה - מחרוזת צינגלה 2026</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-04-03</v>
+      </c>
+      <c r="C13" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410329&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-04-03</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>אליאור נונה - מחרוזת צינגלה 2026</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>אליאב זעפרני - מחרוזת זבקיקו 2026</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-04-03</v>
+      </c>
+      <c r="C14" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410328&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2026-04-03</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v>אליאב זעפרני - מחרוזת זבקיקו 2026</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>אביב לוי - דרום אמריקה</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2026-04-03</v>
+      </c>
+      <c r="C15" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410327&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
+      </c>
+      <c r="D15" t="str">
+        <v>2026-04-03</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <v>אביב לוי - דרום אמריקה</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L15"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-04-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-04-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L12"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שילה שטראל - תקופה שלמה</v>
+        <v>שושנה קנו - סיגריות</v>
       </c>
       <c r="B2" t="str">
         <v>2026-04-03</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410340&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410351&amp;sid=3e18404d100e616166aad5bb56bb617f</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-03</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שילה שטראל - תקופה שלמה</v>
+        <v>שושנה קנו - סיגריות</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>רון סויסה - האור בחשכה</v>
+        <v>רפאל אלוש - שערי שמיים פתח</v>
       </c>
       <c r="B3" t="str">
         <v>2026-04-03</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410339&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410350&amp;sid=3e18404d100e616166aad5bb56bb617f</v>
       </c>
       <c r="D3" t="str">
         <v>2026-04-03</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>רון סויסה - האור בחשכה</v>
+        <v>רפאל אלוש - שערי שמיים פתח</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ישראל בניטה - מי אני</v>
+        <v>יואש - להינשא הלילה</v>
       </c>
       <c r="B4" t="str">
         <v>2026-04-03</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410338&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410349&amp;sid=3e18404d100e616166aad5bb56bb617f</v>
       </c>
       <c r="D4" t="str">
         <v>2026-04-03</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>ישראל בניטה - מי אני</v>
+        <v>יואש - להינשא הלילה</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>יהונתן לוי - הסתכלת לי בעיניים</v>
+        <v>אם סי פיטוסי &amp; לוקץ׳ - אסור ליפול</v>
       </c>
       <c r="B5" t="str">
         <v>2026-04-03</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410337&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410348&amp;sid=3e18404d100e616166aad5bb56bb617f</v>
       </c>
       <c r="D5" t="str">
         <v>2026-04-03</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>יהונתן לוי - הסתכלת לי בעיניים</v>
+        <v>אם סי פיטוסי &amp; לוקץ׳ - אסור ליפול</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>יהונתן חוטה - מחרוזת אבות ובנים 2026</v>
+        <v>אוראל &amp; ויק - צ׳לה בלה</v>
       </c>
       <c r="B6" t="str">
         <v>2026-04-03</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410336&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410347&amp;sid=3e18404d100e616166aad5bb56bb617f</v>
       </c>
       <c r="D6" t="str">
         <v>2026-04-03</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>יהונתן חוטה - מחרוזת אבות ובנים 2026</v>
+        <v>אוראל &amp; ויק - צ׳לה בלה</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>טלי רבקה סימן טוב - חיים חדשים</v>
+        <v>שי פורטוגלי - עד מתי</v>
       </c>
       <c r="B7" t="str">
         <v>2026-04-03</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410335&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410346&amp;sid=3e18404d100e616166aad5bb56bb617f</v>
       </c>
       <c r="D7" t="str">
         <v>2026-04-03</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>טלי רבקה סימן טוב - חיים חדשים</v>
+        <v>שי פורטוגלי - עד מתי</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>חי ברוך &amp; הרב ראובן אלבז - אור של תשובה</v>
+        <v>פרחי ירושלים - ביבי מיקונה</v>
       </c>
       <c r="B8" t="str">
         <v>2026-04-03</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410334&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410345&amp;sid=3e18404d100e616166aad5bb56bb617f</v>
       </c>
       <c r="D8" t="str">
         <v>2026-04-03</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>חי ברוך &amp; הרב ראובן אלבז - אור של תשובה</v>
+        <v>פרחי ירושלים - ביבי מיקונה</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>גל סינואני - יום יפה</v>
+        <v>נעם בוסקילה - והיא שעמדה</v>
       </c>
       <c r="B9" t="str">
         <v>2026-04-03</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410333&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410344&amp;sid=3e18404d100e616166aad5bb56bb617f</v>
       </c>
       <c r="D9" t="str">
         <v>2026-04-03</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>גל סינואני - יום יפה</v>
+        <v>נעם בוסקילה - והיא שעמדה</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>גל אדם - כבר לא שלך</v>
+        <v>מיכאל כורש - בצאת ישראל ממצרים</v>
       </c>
       <c r="B10" t="str">
         <v>2026-04-03</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410332&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410343&amp;sid=3e18404d100e616166aad5bb56bb617f</v>
       </c>
       <c r="D10" t="str">
         <v>2026-04-03</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>גל אדם - כבר לא שלך</v>
+        <v>מיכאל כורש - בצאת ישראל ממצרים</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>בנאל בן ציון - מאשאפ עוד נשימה &amp; היא יודעת</v>
+        <v>דולב הרץ - אהבה</v>
       </c>
       <c r="B11" t="str">
         <v>2026-04-03</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410331&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410342&amp;sid=3e18404d100e616166aad5bb56bb617f</v>
       </c>
       <c r="D11" t="str">
         <v>2026-04-03</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>בנאל בן ציון - מאשאפ עוד נשימה &amp; היא יודעת</v>
+        <v>דולב הרץ - אהבה</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>בועז טביב - מחרוזת ואסיליס קאראס 2026</v>
+        <v>בנימין דנישמן - מחרוזת כורדית 2026</v>
       </c>
       <c r="B12" t="str">
         <v>2026-04-03</v>
       </c>
       <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410330&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410341&amp;sid=3e18404d100e616166aad5bb56bb617f</v>
       </c>
       <c r="D12" t="str">
         <v>2026-04-03</v>
@@ -849,126 +849,12 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>בועז טביב - מחרוזת ואסיליס קאראס 2026</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>אליאור נונה - מחרוזת צינגלה 2026</v>
-      </c>
-      <c r="B13" t="str">
-        <v>2026-04-03</v>
-      </c>
-      <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410329&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
-      </c>
-      <c r="D13" t="str">
-        <v>2026-04-03</v>
-      </c>
-      <c r="E13" t="str">
-        <v/>
-      </c>
-      <c r="F13" t="str">
-        <v/>
-      </c>
-      <c r="G13" t="str">
-        <v/>
-      </c>
-      <c r="H13" t="str">
-        <v/>
-      </c>
-      <c r="I13" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J13" t="str">
-        <v/>
-      </c>
-      <c r="K13" t="str">
-        <v/>
-      </c>
-      <c r="L13" t="str">
-        <v>אליאור נונה - מחרוזת צינגלה 2026</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>אליאב זעפרני - מחרוזת זבקיקו 2026</v>
-      </c>
-      <c r="B14" t="str">
-        <v>2026-04-03</v>
-      </c>
-      <c r="C14" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410328&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
-      </c>
-      <c r="D14" t="str">
-        <v>2026-04-03</v>
-      </c>
-      <c r="E14" t="str">
-        <v/>
-      </c>
-      <c r="F14" t="str">
-        <v/>
-      </c>
-      <c r="G14" t="str">
-        <v/>
-      </c>
-      <c r="H14" t="str">
-        <v/>
-      </c>
-      <c r="I14" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J14" t="str">
-        <v/>
-      </c>
-      <c r="K14" t="str">
-        <v/>
-      </c>
-      <c r="L14" t="str">
-        <v>אליאב זעפרני - מחרוזת זבקיקו 2026</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>אביב לוי - דרום אמריקה</v>
-      </c>
-      <c r="B15" t="str">
-        <v>2026-04-03</v>
-      </c>
-      <c r="C15" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410327&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
-      </c>
-      <c r="D15" t="str">
-        <v>2026-04-03</v>
-      </c>
-      <c r="E15" t="str">
-        <v/>
-      </c>
-      <c r="F15" t="str">
-        <v/>
-      </c>
-      <c r="G15" t="str">
-        <v/>
-      </c>
-      <c r="H15" t="str">
-        <v/>
-      </c>
-      <c r="I15" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J15" t="str">
-        <v/>
-      </c>
-      <c r="K15" t="str">
-        <v/>
-      </c>
-      <c r="L15" t="str">
-        <v>אביב לוי - דרום אמריקה</v>
+        <v>בנימין דנישמן - מחרוזת כורדית 2026</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L12"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-04-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-04-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שושנה קנו - סיגריות</v>
+        <v>מניפסט גם זו לטובה</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-03</v>
+        <v>2026-04-04</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410351&amp;sid=3e18404d100e616166aad5bb56bb617f</v>
+        <v>https://yosmusic.com/%d7%9e%d7%a0%d7%99%d7%a4%d7%a1%d7%98-%d7%92%d7%9d-%d7%96%d7%95-%d7%9c%d7%98%d7%95%d7%91%d7%94/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-03</v>
+        <v>2026-04-04</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>השיר "גם זו לטובה" של סהר שרה מוסרי (מתוך הפרויקט “מניפסט”) הוא שיר פופ קצבי שמבצע מהלך מעניין: הוא לוקח מציאות יומיומית עמוסת חרדה, תסכול ולחץ, ומנסה להפוך אותה למנטרה של חשיבה חיובית. הכותבת משתמשת ב“גם זו לטובה” כטכניקה מנטלית. המשפט</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,392 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שושנה קנו - סיגריות</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>רפאל אלוש - שערי שמיים פתח</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-04-03</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410350&amp;sid=3e18404d100e616166aad5bb56bb617f</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-04-03</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>רפאל אלוש - שערי שמיים פתח</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>יואש - להינשא הלילה</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-04-03</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410349&amp;sid=3e18404d100e616166aad5bb56bb617f</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-04-03</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>יואש - להינשא הלילה</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>אם סי פיטוסי &amp; לוקץ׳ - אסור ליפול</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-04-03</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410348&amp;sid=3e18404d100e616166aad5bb56bb617f</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-04-03</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>אם סי פיטוסי &amp; לוקץ׳ - אסור ליפול</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>אוראל &amp; ויק - צ׳לה בלה</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-04-03</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410347&amp;sid=3e18404d100e616166aad5bb56bb617f</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-04-03</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>אוראל &amp; ויק - צ׳לה בלה</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>שי פורטוגלי - עד מתי</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-04-03</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410346&amp;sid=3e18404d100e616166aad5bb56bb617f</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-04-03</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>שי פורטוגלי - עד מתי</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>פרחי ירושלים - ביבי מיקונה</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-04-03</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410345&amp;sid=3e18404d100e616166aad5bb56bb617f</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-04-03</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>פרחי ירושלים - ביבי מיקונה</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>נעם בוסקילה - והיא שעמדה</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-04-03</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410344&amp;sid=3e18404d100e616166aad5bb56bb617f</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-04-03</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>נעם בוסקילה - והיא שעמדה</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>מיכאל כורש - בצאת ישראל ממצרים</v>
-      </c>
-      <c r="B10" t="str">
-        <v>2026-04-03</v>
-      </c>
-      <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410343&amp;sid=3e18404d100e616166aad5bb56bb617f</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2026-04-03</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v>מיכאל כורש - בצאת ישראל ממצרים</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>דולב הרץ - אהבה</v>
-      </c>
-      <c r="B11" t="str">
-        <v>2026-04-03</v>
-      </c>
-      <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410342&amp;sid=3e18404d100e616166aad5bb56bb617f</v>
-      </c>
-      <c r="D11" t="str">
-        <v>2026-04-03</v>
-      </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J11" t="str">
-        <v/>
-      </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
-      <c r="L11" t="str">
-        <v>דולב הרץ - אהבה</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>בנימין דנישמן - מחרוזת כורדית 2026</v>
-      </c>
-      <c r="B12" t="str">
-        <v>2026-04-03</v>
-      </c>
-      <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410341&amp;sid=3e18404d100e616166aad5bb56bb617f</v>
-      </c>
-      <c r="D12" t="str">
-        <v>2026-04-03</v>
-      </c>
-      <c r="E12" t="str">
-        <v/>
-      </c>
-      <c r="F12" t="str">
-        <v/>
-      </c>
-      <c r="G12" t="str">
-        <v/>
-      </c>
-      <c r="H12" t="str">
-        <v/>
-      </c>
-      <c r="I12" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J12" t="str">
-        <v/>
-      </c>
-      <c r="K12" t="str">
-        <v/>
-      </c>
-      <c r="L12" t="str">
-        <v>בנימין דנישמן - מחרוזת כורדית 2026</v>
+        <v>מניפסט גם זו לטובה</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-04-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-04-week01/titles.xlsx
@@ -436,7 +436,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מניפסט גם זו לטובה</v>
+        <v>מניפסט – גם זו לטובה</v>
       </c>
       <c r="B2" t="str">
         <v>2026-04-04</v>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מניפסט גם זו לטובה</v>
+        <v>מניפסט – גם זו לטובה</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/global/2026-04-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-04-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מניפסט – גם זו לטובה</v>
+        <v>שירז אברהם - שונא אותך</v>
       </c>
       <c r="B2" t="str">
         <v>2026-04-04</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%a0%d7%99%d7%a4%d7%a1%d7%98-%d7%92%d7%9d-%d7%96%d7%95-%d7%9c%d7%98%d7%95%d7%91%d7%94/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410360&amp;sid=cc30946d1b11e3c89cd1b1bb4e38313b</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-04</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר "גם זו לטובה" של סהר שרה מוסרי (מתוך הפרויקט “מניפסט”) הוא שיר פופ קצבי שמבצע מהלך מעניין: הוא לוקח מציאות יומיומית עמוסת חרדה, תסכול ולחץ, ומנסה להפוך אותה למנטרה של חשיבה חיובית. הכותבת משתמשת ב“גם זו לטובה” כטכניקה מנטלית. המשפט</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,164 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מניפסט – גם זו לטובה</v>
+        <v>שירז אברהם - שונא אותך</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>שגיא גטר - מקולל</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-04-04</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410359&amp;sid=cc30946d1b11e3c89cd1b1bb4e38313b</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-04-04</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>שגיא גטר - מקולל</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>עמירן דביר מארח את אהרל׳ה סמט וגדעון לוי - למענך עשה</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-04-04</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410358&amp;sid=cc30946d1b11e3c89cd1b1bb4e38313b</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-04-04</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>עמירן דביר מארח את אהרל׳ה סמט וגדעון לוי - למענך עשה</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>ישראל דיין - מחרוזת שקטים 2026</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-04-04</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410355&amp;sid=cc30946d1b11e3c89cd1b1bb4e38313b</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-04-04</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>ישראל דיין - מחרוזת שקטים 2026</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>חנן בן ארי &amp; פאר טסי - הלוואי</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-04-04</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410354&amp;sid=cc30946d1b11e3c89cd1b1bb4e38313b</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-04-04</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>חנן בן ארי &amp; פאר טסי - הלוואי</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L6"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-04-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-04-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שירז אברהם - שונא אותך</v>
+        <v>חנן בן ארי ופאר טסי – הלוואי</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-04</v>
+        <v>2026-04-05</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410360&amp;sid=cc30946d1b11e3c89cd1b1bb4e38313b</v>
+        <v>https://yosmusic.com/%d7%97%d7%a0%d7%9f-%d7%91%d7%9f-%d7%90%d7%a8%d7%99-%d7%95%d7%a4%d7%90%d7%a8-%d7%98%d7%a1%d7%99-%d7%94%d7%9c%d7%95%d7%95%d7%90%d7%99/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-04</v>
+        <v>2026-04-05</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>השיר ששרים בדואט חנן בן ארי ופאר טסי הנבנה כמענה רגשי קולקטיבי למציאות של משבר, ובמיוחד על רקע תקופות מתוחות כמו מלחמה. המילה “הלוואי” שחוזרת כמעט באובססיביות אינה עמדה אלא משאלה אקראית. השיר לא מתיימר לפתור אלא לבטא כמיהה פשוטה</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,27 +469,27 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שירז אברהם - שונא אותך</v>
+        <v>חנן בן ארי ופאר טסי – הלוואי</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>שגיא גטר - מקולל</v>
+        <v>אבנר טואג – מי אני מה אני מה אני עושה פה</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-04-04</v>
+        <v>2026-04-05</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410359&amp;sid=cc30946d1b11e3c89cd1b1bb4e38313b</v>
+        <v>https://yosmusic.com/%d7%90%d7%91%d7%a0%d7%a8-%d7%98%d7%95%d7%90%d7%92-%d7%9e%d7%99-%d7%90%d7%a0%d7%99-%d7%9e%d7%94-%d7%90%d7%a0%d7%99-%d7%9e%d7%94-%d7%90%d7%a0%d7%99-%d7%a2%d7%95%d7%a9%d7%94-%d7%a4%d7%94/</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-04-04</v>
+        <v>2026-04-05</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>אבנר טואג מצליח לקחת שאלה פילוסופית כמעט קלאסית – זהות ומשמעות ולתרגם אותה לחוויה מוזיקלית עכשווית, אישית ונגישה. "מי אני מה אני מה אני עושה פה” – זו אינה רק שאלה אקראית אלא הצפה, בלבול, ניסיון לאחוז במשהו יציב השיר</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -507,126 +507,12 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>שגיא גטר - מקולל</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>עמירן דביר מארח את אהרל׳ה סמט וגדעון לוי - למענך עשה</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-04-04</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410358&amp;sid=cc30946d1b11e3c89cd1b1bb4e38313b</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-04-04</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>עמירן דביר מארח את אהרל׳ה סמט וגדעון לוי - למענך עשה</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>ישראל דיין - מחרוזת שקטים 2026</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-04-04</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410355&amp;sid=cc30946d1b11e3c89cd1b1bb4e38313b</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-04-04</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>ישראל דיין - מחרוזת שקטים 2026</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>חנן בן ארי &amp; פאר טסי - הלוואי</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-04-04</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410354&amp;sid=cc30946d1b11e3c89cd1b1bb4e38313b</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-04-04</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>חנן בן ארי &amp; פאר טסי - הלוואי</v>
+        <v>אבנר טואג – מי אני מה אני מה אני עושה פה</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-04-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-04-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>חנן בן ארי ופאר טסי – הלוואי</v>
+        <v>אלעד אביבי - יהודי זה נשמה</v>
       </c>
       <c r="B2" t="str">
         <v>2026-04-05</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%97%d7%a0%d7%9f-%d7%91%d7%9f-%d7%90%d7%a8%d7%99-%d7%95%d7%a4%d7%90%d7%a8-%d7%98%d7%a1%d7%99-%d7%94%d7%9c%d7%95%d7%95%d7%90%d7%99/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410375&amp;sid=77f23f31065bb4ab90b9297067773482</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-05</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר ששרים בדואט חנן בן ארי ופאר טסי הנבנה כמענה רגשי קולקטיבי למציאות של משבר, ובמיוחד על רקע תקופות מתוחות כמו מלחמה. המילה “הלוואי” שחוזרת כמעט באובססיביות אינה עמדה אלא משאלה אקראית. השיר לא מתיימר לפתור אלא לבטא כמיהה פשוטה</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>חנן בן ארי ופאר טסי – הלוואי</v>
+        <v>אלעד אביבי - יהודי זה נשמה</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>אבנר טואג – מי אני מה אני מה אני עושה פה</v>
+        <v>אבימאיר - תגידי לנו כן</v>
       </c>
       <c r="B3" t="str">
         <v>2026-04-05</v>
       </c>
       <c r="C3" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%91%d7%a0%d7%a8-%d7%98%d7%95%d7%90%d7%92-%d7%9e%d7%99-%d7%90%d7%a0%d7%99-%d7%9e%d7%94-%d7%90%d7%a0%d7%99-%d7%9e%d7%94-%d7%90%d7%a0%d7%99-%d7%a2%d7%95%d7%a9%d7%94-%d7%a4%d7%94/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410374&amp;sid=77f23f31065bb4ab90b9297067773482</v>
       </c>
       <c r="D3" t="str">
         <v>2026-04-05</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>אבנר טואג מצליח לקחת שאלה פילוסופית כמעט קלאסית – זהות ומשמעות ולתרגם אותה לחוויה מוזיקלית עכשווית, אישית ונגישה. "מי אני מה אני מה אני עושה פה” – זו אינה רק שאלה אקראית אלא הצפה, בלבול, ניסיון לאחוז במשהו יציב השיר</v>
+        <v/>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -507,12 +507,240 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>אבנר טואג – מי אני מה אני מה אני עושה פה</v>
+        <v>אבימאיר - תגידי לנו כן</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>סאלי - שתי נשמות</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-04-05</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410373&amp;sid=77f23f31065bb4ab90b9297067773482</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-04-05</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>סאלי - שתי נשמות</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>ניר בנילוש - מכור לדיכאון</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-04-05</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410372&amp;sid=77f23f31065bb4ab90b9297067773482</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-04-05</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>ניר בנילוש - מכור לדיכאון</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>התקווה 6 - חופשת מלחמה</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-04-05</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410371&amp;sid=77f23f31065bb4ab90b9297067773482</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-04-05</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>התקווה 6 - חופשת מלחמה</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>הלהקות הצבאיות - שיר הלהקה 2026</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-04-05</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410370&amp;sid=77f23f31065bb4ab90b9297067773482</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-04-05</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>הלהקות הצבאיות - שיר הלהקה 2026</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>דן ביטון - לא משנה מה תגיד</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-04-05</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410369&amp;sid=77f23f31065bb4ab90b9297067773482</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-04-05</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>דן ביטון - לא משנה מה תגיד</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>בן לוי &amp; לי שי - אותו דבר</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-04-05</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410368&amp;sid=77f23f31065bb4ab90b9297067773482</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-04-05</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>בן לוי &amp; לי שי - אותו דבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-04-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-04-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אלעד אביבי - יהודי זה נשמה</v>
+        <v>ילד – חבלמאוד (שאנילאיכולהיותאישה)</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-05</v>
+        <v>2026-04-06</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410375&amp;sid=77f23f31065bb4ab90b9297067773482</v>
+        <v>https://yosmusic.com/%d7%99%d7%9c%d7%93-%d7%97%d7%91%d7%9c%d7%9e%d7%90%d7%95%d7%93-%d7%a9%d7%90%d7%a0%d7%99%d7%9c%d7%90%d7%99%d7%9b%d7%95%d7%9c%d7%94%d7%99%d7%95%d7%aa%d7%90%d7%99%d7%a9%d7%94/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-05</v>
+        <v>2026-04-06</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>השיר "חבל מאוד (שאני לא יכול להיות אישה)" של עומר יפת (והרכב "ילד") הוא שיר רוקנרולי מהיר, כמעט כאוטי, שמשתמש בהומור, חזרתיות והגזמה כדי לפרק ולהרכיב מחדש תפיסות של מגדר, זהות ודימוי עצמי. הקצב המהיר והחזרות המרובות יוצרים תחושת אובססיה</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,278 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אלעד אביבי - יהודי זה נשמה</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>אבימאיר - תגידי לנו כן</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-04-05</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410374&amp;sid=77f23f31065bb4ab90b9297067773482</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-04-05</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>אבימאיר - תגידי לנו כן</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>סאלי - שתי נשמות</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-04-05</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410373&amp;sid=77f23f31065bb4ab90b9297067773482</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-04-05</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>סאלי - שתי נשמות</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>ניר בנילוש - מכור לדיכאון</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-04-05</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410372&amp;sid=77f23f31065bb4ab90b9297067773482</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-04-05</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>ניר בנילוש - מכור לדיכאון</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>התקווה 6 - חופשת מלחמה</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-04-05</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410371&amp;sid=77f23f31065bb4ab90b9297067773482</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-04-05</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>התקווה 6 - חופשת מלחמה</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>הלהקות הצבאיות - שיר הלהקה 2026</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-04-05</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410370&amp;sid=77f23f31065bb4ab90b9297067773482</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-04-05</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>הלהקות הצבאיות - שיר הלהקה 2026</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>דן ביטון - לא משנה מה תגיד</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-04-05</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410369&amp;sid=77f23f31065bb4ab90b9297067773482</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-04-05</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>דן ביטון - לא משנה מה תגיד</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>בן לוי &amp; לי שי - אותו דבר</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-04-05</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410368&amp;sid=77f23f31065bb4ab90b9297067773482</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-04-05</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>בן לוי &amp; לי שי - אותו דבר</v>
+        <v>ילד – חבלמאוד (שאנילאיכולהיותאישה)</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-04-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-04-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ילד – חבלמאוד (שאנילאיכולהיותאישה)</v>
+        <v>שלווה - ילדה טובה</v>
       </c>
       <c r="B2" t="str">
         <v>2026-04-06</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%99%d7%9c%d7%93-%d7%97%d7%91%d7%9c%d7%9e%d7%90%d7%95%d7%93-%d7%a9%d7%90%d7%a0%d7%99%d7%9c%d7%90%d7%99%d7%9b%d7%95%d7%9c%d7%94%d7%99%d7%95%d7%aa%d7%90%d7%99%d7%a9%d7%94/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410385&amp;sid=563f0dd190cfae43c1a34d1a696bd38a</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-06</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר "חבל מאוד (שאני לא יכול להיות אישה)" של עומר יפת (והרכב "ילד") הוא שיר רוקנרולי מהיר, כמעט כאוטי, שמשתמש בהומור, חזרתיות והגזמה כדי לפרק ולהרכיב מחדש תפיסות של מגדר, זהות ודימוי עצמי. הקצב המהיר והחזרות המרובות יוצרים תחושת אובססיה</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,278 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ילד – חבלמאוד (שאנילאיכולהיותאישה)</v>
+        <v>שלווה - ילדה טובה</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>צוף מימון &amp; יקיר - נוף אחר</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-04-06</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410384&amp;sid=563f0dd190cfae43c1a34d1a696bd38a</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-04-06</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>צוף מימון &amp; יקיר - נוף אחר</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>יגל יובל שרעבי - מיליונר</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-04-06</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410383&amp;sid=563f0dd190cfae43c1a34d1a696bd38a</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-04-06</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>יגל יובל שרעבי - מיליונר</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>דבורה מונצרש - לגדול מתוך הנס (שירת נשים)</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-04-06</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410381&amp;sid=563f0dd190cfae43c1a34d1a696bd38a</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-04-06</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>דבורה מונצרש - לגדול מתוך הנס (שירת נשים)</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>בבויה - אף אחד</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-04-06</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410380&amp;sid=563f0dd190cfae43c1a34d1a696bd38a</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-04-06</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>בבויה - אף אחד</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>באני - טבעת</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-04-06</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410379&amp;sid=563f0dd190cfae43c1a34d1a696bd38a</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-04-06</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>באני - טבעת</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>אדיר ניזרי - מחרוזת בית״ר זה עד המוות 2026</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-04-06</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410378&amp;sid=563f0dd190cfae43c1a34d1a696bd38a</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-04-06</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>אדיר ניזרי - מחרוזת בית״ר זה עד המוות 2026</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>נסרין קדרי – יהלום מעבדה</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-04-06</v>
+      </c>
+      <c r="C9" t="str">
+        <v>https://yosmusic.com/%d7%a0%d7%a1%d7%a8%d7%99%d7%9f-%d7%a7%d7%93%d7%a8%d7%99-%d7%99%d7%94%d7%9c%d7%95%d7%9d-%d7%9e%d7%a2%d7%91%d7%93%d7%94/</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-04-06</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v>השיר "יהלום מעבדה" מציג את הפרסונה העכשווית של נסרין קדר, שיר חפלה שמאמץ במודע אסתטיקה "נמוכה", פרובוקטיבית ומוגזמת, כדי לייצר גם בידור וגם ביקורת חברתית גם אם לא תמיד ברור עד כמה הביקורת מכוונת. השיר מפרק את הפנטזיה של זיווג</v>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>נסרין קדרי – יהלום מעבדה</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-04-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-04-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שלווה - ילדה טובה</v>
+        <v>אריה פרננד - פעם היו זמנים</v>
       </c>
       <c r="B2" t="str">
         <v>2026-04-06</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410385&amp;sid=563f0dd190cfae43c1a34d1a696bd38a</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410390&amp;sid=66e62fcdd2c9ce707ca8edc22bf3960b</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-06</v>
+        <v>2026-04-07</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שלווה - ילדה טובה</v>
+        <v>אריה פרננד - פעם היו זמנים</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>צוף מימון &amp; יקיר - נוף אחר</v>
+        <v>עודד מנשרי - עד שיאיר הבוקר</v>
       </c>
       <c r="B3" t="str">
         <v>2026-04-06</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410384&amp;sid=563f0dd190cfae43c1a34d1a696bd38a</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410389&amp;sid=66e62fcdd2c9ce707ca8edc22bf3960b</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-04-06</v>
+        <v>2026-04-07</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>צוף מימון &amp; יקיר - נוף אחר</v>
+        <v>עודד מנשרי - עד שיאיר הבוקר</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>יגל יובל שרעבי - מיליונר</v>
+        <v>דוד וייה - הכל היה זמני</v>
       </c>
       <c r="B4" t="str">
         <v>2026-04-06</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410383&amp;sid=563f0dd190cfae43c1a34d1a696bd38a</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410388&amp;sid=66e62fcdd2c9ce707ca8edc22bf3960b</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-04-06</v>
+        <v>2026-04-07</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,202 +545,12 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>יגל יובל שרעבי - מיליונר</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>דבורה מונצרש - לגדול מתוך הנס (שירת נשים)</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-04-06</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410381&amp;sid=563f0dd190cfae43c1a34d1a696bd38a</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-04-06</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>דבורה מונצרש - לגדול מתוך הנס (שירת נשים)</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>בבויה - אף אחד</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-04-06</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410380&amp;sid=563f0dd190cfae43c1a34d1a696bd38a</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-04-06</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>בבויה - אף אחד</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>באני - טבעת</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-04-06</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410379&amp;sid=563f0dd190cfae43c1a34d1a696bd38a</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-04-06</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>באני - טבעת</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>אדיר ניזרי - מחרוזת בית״ר זה עד המוות 2026</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-04-06</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410378&amp;sid=563f0dd190cfae43c1a34d1a696bd38a</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-04-06</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>אדיר ניזרי - מחרוזת בית״ר זה עד המוות 2026</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>נסרין קדרי – יהלום מעבדה</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-04-06</v>
-      </c>
-      <c r="C9" t="str">
-        <v>https://yosmusic.com/%d7%a0%d7%a1%d7%a8%d7%99%d7%9f-%d7%a7%d7%93%d7%a8%d7%99-%d7%99%d7%94%d7%9c%d7%95%d7%9d-%d7%9e%d7%a2%d7%91%d7%93%d7%94/</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-04-06</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v>השיר "יהלום מעבדה" מציג את הפרסונה העכשווית של נסרין קדר, שיר חפלה שמאמץ במודע אסתטיקה "נמוכה", פרובוקטיבית ומוגזמת, כדי לייצר גם בידור וגם ביקורת חברתית גם אם לא תמיד ברור עד כמה הביקורת מכוונת. השיר מפרק את הפנטזיה של זיווג</v>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>נסרין קדרי – יהלום מעבדה</v>
+        <v>דוד וייה - הכל היה זמני</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-04-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-04-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אריה פרננד - פעם היו זמנים</v>
+        <v>ישי ריבו – לא לחינם</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-06</v>
+        <v>2026-04-07</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410390&amp;sid=66e62fcdd2c9ce707ca8edc22bf3960b</v>
+        <v>https://yosmusic.com/%d7%99%d7%a9%d7%99-%d7%a8%d7%99%d7%91%d7%95-%d7%9c%d7%90-%d7%9c%d7%97%d7%99%d7%a0%d7%9d/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-07</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>ישי ריבו שר שיר מורכב שמשלב את סגנונו האמוני  עם מבנה מודרני ומגוון, הכולל גם פזמון מלודי ובתים בסגנון ראפ. השיר עוסק בכמה שכבות מרכזיות: אדם מול יצרו – "עושה היצר זבלו אוצר / גאון הדור בשיווק מוצר" הריבוי בין</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,88 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אריה פרננד - פעם היו זמנים</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>עודד מנשרי - עד שיאיר הבוקר</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-04-06</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410389&amp;sid=66e62fcdd2c9ce707ca8edc22bf3960b</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-04-07</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>עודד מנשרי - עד שיאיר הבוקר</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>דוד וייה - הכל היה זמני</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-04-06</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410388&amp;sid=66e62fcdd2c9ce707ca8edc22bf3960b</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-04-07</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>דוד וייה - הכל היה זמני</v>
+        <v>ישי ריבו – לא לחינם</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>